--- a/docs/matrizreqs.xlsx
+++ b/docs/matrizreqs.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="90">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -40,7 +40,7 @@
     <t xml:space="preserve">empleado</t>
   </si>
   <si>
-    <t xml:space="preserve">Emplea 2</t>
+    <t xml:space="preserve">sprempleado</t>
   </si>
   <si>
     <t xml:space="preserve">gerente</t>
@@ -88,6 +88,9 @@
     <t xml:space="preserve">crear usuarios</t>
   </si>
   <si>
+    <t xml:space="preserve">gestionar seguridad para que no se pueda poner rol admin</t>
+  </si>
+  <si>
     <t xml:space="preserve">Seg 05</t>
   </si>
   <si>
@@ -287,39 +290,6 @@
   </si>
   <si>
     <t xml:space="preserve">elimnar cxp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gestion de roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rol 01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">registrar rol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gestionar seguridad para que no se pueda poner rol admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rol 02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ver rol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rol 03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">actualizar rol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rol 04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">elimnar rol</t>
   </si>
 </sst>
 </file>
@@ -329,12 +299,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -351,15 +322,8 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
-    <font>
-      <i val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-    </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -386,8 +350,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBF819E"/>
-        <bgColor rgb="FFEC9BA4"/>
+        <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
     <fill>
@@ -424,18 +394,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF5EB91E"/>
         <bgColor rgb="FF808000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC9BA4"/>
-        <bgColor rgb="FFFF8080"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -487,7 +445,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -524,47 +482,47 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -576,28 +534,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -648,7 +590,7 @@
       <rgbColor rgb="FFA8D08D"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF9CC2E5"/>
-      <rgbColor rgb="FFEC9BA4"/>
+      <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFB4C7DC"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
@@ -792,7 +734,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="7.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="10" style="1" width="10.66"/>
   </cols>
@@ -930,16 +873,21 @@
       <c r="I6" s="8" t="s">
         <v>13</v>
       </c>
+      <c r="J6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="7"/>
       <c r="D7" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -949,16 +897,19 @@
       <c r="I7" s="8" t="s">
         <v>13</v>
       </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="7"/>
       <c r="D8" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -968,16 +919,19 @@
       <c r="I8" s="8" t="s">
         <v>13</v>
       </c>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="7"/>
       <c r="D9" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -985,16 +939,19 @@
       <c r="I9" s="8" t="s">
         <v>13</v>
       </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="7"/>
       <c r="D10" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -1010,10 +967,10 @@
       <c r="B11" s="4"/>
       <c r="C11" s="7"/>
       <c r="D11" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
@@ -1025,587 +982,511 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="C12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="D12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="10" t="s">
+      <c r="E12" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="10" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="10" t="s">
+      <c r="E13" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="10" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="10" t="s">
+      <c r="E14" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10" t="s">
+      <c r="E15" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="11" t="s">
+      <c r="B16" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="C16" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="12" t="s">
+      <c r="E16" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="12" t="s">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="12" t="s">
+      <c r="E17" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="12" t="s">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="12" t="s">
+      <c r="E18" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="12" t="s">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12" t="s">
+      <c r="E19" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="n">
+      <c r="A20" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="14" t="s">
+      <c r="B20" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="C20" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="D20" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="15" t="s">
+      <c r="E20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="15" t="s">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="15" t="s">
+      <c r="E21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="15" t="s">
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="15" t="s">
+      <c r="E22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" s="15" t="s">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15" t="s">
+      <c r="E23" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="16" t="s">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="D24" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="16" t="s">
-        <v>13</v>
-      </c>
+      <c r="E24" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="16" t="s">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="16" t="s">
-        <v>13</v>
-      </c>
+      <c r="E25" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="16" t="s">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>13</v>
-      </c>
+      <c r="E26" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" s="16" t="s">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16" t="s">
-        <v>13</v>
-      </c>
+      <c r="E27" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="18" t="s">
+      <c r="B28" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="C28" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="D28" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="19" t="s">
+      <c r="E28" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E29" s="19" t="s">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="19" t="s">
+      <c r="E29" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" s="19" t="s">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="I30" s="19" t="s">
+      <c r="E30" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="E31" s="19" t="s">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19" t="s">
+      <c r="E31" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B32" s="18"/>
-      <c r="C32" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="E32" s="21" t="s">
+      <c r="B32" s="20"/>
+      <c r="C32" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="F32" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="21" t="s">
+      <c r="E32" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="23" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="E33" s="21" t="s">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="21" t="s">
+      <c r="E33" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="23" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="E34" s="21" t="s">
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I34" s="21" t="s">
+      <c r="E34" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="23" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="E35" s="21" t="s">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="B36" s="23" t="s">
+      <c r="E35" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="E36" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="J36" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="K36" s="27"/>
-      <c r="L36" s="27"/>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="E37" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="I37" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="E38" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="27"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="27"/>
-    </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="E39" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="J39" s="27"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="27"/>
-    </row>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2544,10 +2425,10 @@
     <row r="975" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="976" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="977" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="978" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="979" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="980" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="981" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2571,7 +2452,7 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="26">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2582,6 +2463,7 @@
     <mergeCell ref="B3:B11"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="C6:C11"/>
+    <mergeCell ref="J6:L9"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="C12:C15"/>
@@ -2597,10 +2479,6 @@
     <mergeCell ref="B28:B35"/>
     <mergeCell ref="C28:C31"/>
     <mergeCell ref="C32:C35"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="C36:C39"/>
-    <mergeCell ref="J36:L39"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
